--- a/20260914-your-country-s-label-is-not-yours/belindia_replication_output.xlsx
+++ b/20260914-your-country-s-label-is-not-yours/belindia_replication_output.xlsx
@@ -459,7 +459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>One sheet per table in the post. Every sheet is also written as a csv. Method and conventions are documented in the script header.</t>
+          <t>One sheet per table in the post. The country results sheet is also written as belindia_country-results.csv. Method and conventions are documented in the script header.</t>
         </is>
       </c>
     </row>
